--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566828816</v>
+        <v>46157.93093911892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093911892</v>
+        <v>46157.93170865325</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170865325</v>
+        <v>46157.93398654959</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398654959</v>
+        <v>46157.93716393588</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716393588</v>
+        <v>46158.28215006892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28215006892</v>
+        <v>46158.29676488832</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676488832</v>
+        <v>46158.29813104256</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813104256</v>
+        <v>46158.33385972009</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385972009</v>
+        <v>46158.36855749366</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855749366</v>
+        <v>46158.37286463968</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
